--- a/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-ti-flow-di-ga-close-operation-input.xlsx
+++ b/tiflow-diga/develop/2.0.0-ballot.2/StructureDefinition-ti-flow-di-ga-close-operation-input.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1290" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1294" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,6 +383,10 @@
     <t>closed</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 inv-1:A parameter must have one and only one of (value, resource, part) {(part.exists() and value.empty() and resource.empty()) or (part.empty() and (value.exists() xor resource.exists()))}</t>
   </si>
@@ -423,6 +427,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -462,6 +476,9 @@
     <t>The name of the parameter (reference to the operation definition).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Parameters.parameter.value[x]</t>
   </si>
   <si>
@@ -475,24 +492,31 @@
     <t>If the parameter is a data type.</t>
   </si>
   <si>
+    <t>ele-1
+inv-1</t>
+  </si>
+  <si>
+    <t>Parameters.parameter.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>If parameter is a whole resource</t>
+  </si>
+  <si>
+    <t>If the parameter is a whole resource.</t>
+  </si>
+  <si>
+    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+  </si>
+  <si>
     <t xml:space="preserve">inv-1
 </t>
   </si>
   <si>
-    <t>Parameters.parameter.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>If parameter is a whole resource</t>
-  </si>
-  <si>
-    <t>If the parameter is a whole resource.</t>
-  </si>
-  <si>
-    <t>When resolving references in resources, the operation definition may specify how references may be resolved between parameters. If a reference cannot be resolved between the parameters, the application should fall back to it's general resource resolution methods.</t>
+    <t>Entity. Role, or Act</t>
   </si>
   <si>
     <t>Parameters.parameter.part</t>
@@ -965,7 +989,7 @@
     <col min="26" max="26" width="35.15234375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1722,24 +1746,24 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1762,13 +1786,13 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1819,7 +1843,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -1842,14 +1866,14 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1868,16 +1892,16 @@
         <v>76</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1915,19 +1939,19 @@
         <v>76</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC9" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -1939,7 +1963,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -1950,14 +1974,14 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -1976,19 +2000,19 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O10" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P10" t="s" s="2">
         <v>76</v>
@@ -2037,7 +2061,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2049,21 +2073,21 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2086,15 +2110,17 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>76</v>
@@ -2143,7 +2169,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>85</v>
@@ -2166,10 +2192,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2192,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2249,7 +2275,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2258,7 +2284,7 @@
         <v>85</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>97</v>
@@ -2267,15 +2293,15 @@
         <v>76</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2298,16 +2324,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2357,7 +2383,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -2366,7 +2392,7 @@
         <v>85</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>76</v>
@@ -2375,15 +2401,15 @@
         <v>76</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2409,13 +2435,13 @@
         <v>76</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2465,7 +2491,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2477,7 +2503,7 @@
         <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>76</v>
@@ -2486,15 +2512,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>113</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>76</v>
@@ -2507,7 +2533,7 @@
         <v>85</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>76</v>
@@ -2582,24 +2608,24 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>119</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2622,13 +2648,13 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2679,7 +2705,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2702,14 +2728,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -2728,16 +2754,16 @@
         <v>76</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2775,19 +2801,19 @@
         <v>76</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2799,7 +2825,7 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>76</v>
@@ -2810,14 +2836,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2836,19 +2862,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -2897,7 +2923,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -2909,21 +2935,21 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2946,15 +2972,17 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N19" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>76</v>
@@ -2964,7 +2992,7 @@
         <v>76</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="T19" t="s" s="2">
         <v>76</v>
@@ -3003,7 +3031,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>85</v>
@@ -3026,10 +3054,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3052,13 +3080,13 @@
         <v>86</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3109,7 +3137,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3118,7 +3146,7 @@
         <v>85</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>97</v>
@@ -3127,15 +3155,15 @@
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3158,16 +3186,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3217,7 +3245,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3226,7 +3254,7 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>76</v>
@@ -3235,15 +3263,15 @@
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3269,13 +3297,13 @@
         <v>76</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3323,7 +3351,7 @@
         <v>118</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -3335,7 +3363,7 @@
         <v>76</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>76</v>
@@ -3346,10 +3374,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3372,13 +3400,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3429,7 +3457,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -3452,14 +3480,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -3478,16 +3506,16 @@
         <v>76</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3525,19 +3553,19 @@
         <v>76</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -3549,7 +3577,7 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
@@ -3560,14 +3588,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3586,19 +3614,19 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>76</v>
@@ -3647,7 +3675,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -3659,21 +3687,21 @@
         <v>76</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3696,15 +3724,17 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>76</v>
@@ -3753,7 +3783,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>85</v>
@@ -3776,10 +3806,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3802,13 +3832,13 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3859,7 +3889,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -3868,7 +3898,7 @@
         <v>85</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>97</v>
@@ -3877,15 +3907,15 @@
         <v>76</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3908,16 +3938,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3967,7 +3997,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -3976,7 +4006,7 @@
         <v>85</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>76</v>
@@ -3985,15 +4015,15 @@
         <v>76</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>76</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4019,13 +4049,13 @@
         <v>76</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4075,7 +4105,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4087,7 +4117,7 @@
         <v>76</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
@@ -4096,15 +4126,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>76</v>
@@ -4117,7 +4147,7 @@
         <v>85</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>76</v>
@@ -4129,13 +4159,13 @@
         <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4185,7 +4215,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4197,7 +4227,7 @@
         <v>76</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
@@ -4208,10 +4238,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4234,13 +4264,13 @@
         <v>76</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4291,7 +4321,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -4314,14 +4344,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4340,16 +4370,16 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4387,19 +4417,19 @@
         <v>76</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>76</v>
+        <v>132</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>76</v>
+        <v>133</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -4411,7 +4441,7 @@
         <v>76</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>76</v>
@@ -4422,14 +4452,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -4448,19 +4478,19 @@
         <v>86</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>76</v>
@@ -4509,7 +4539,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -4521,21 +4551,21 @@
         <v>76</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4558,15 +4588,17 @@
         <v>86</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>146</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -4576,7 +4608,7 @@
         <v>76</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>76</v>
@@ -4615,7 +4647,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>85</v>
@@ -4638,10 +4670,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4664,13 +4696,13 @@
         <v>86</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4721,7 +4753,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -4730,7 +4762,7 @@
         <v>85</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>97</v>
@@ -4739,15 +4771,15 @@
         <v>76</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4770,16 +4802,16 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4829,7 +4861,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -4847,15 +4879,15 @@
         <v>76</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>191</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4881,13 +4913,13 @@
         <v>76</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4937,7 +4969,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -4949,7 +4981,7 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
